--- a/nr-update-patient-name/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/nr-update-patient-name/ig/StructureDefinition-fr-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5313" uniqueCount="687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5308" uniqueCount="685">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T13:41:02+00:00</t>
+    <t>2025-02-17T10:02:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1012,12 +1012,6 @@
     &lt;code value="NH"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
     <t>Patient.identifier:NSS.system</t>
@@ -7391,11 +7385,9 @@
       <c r="X42" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="Y42" t="s" s="2">
-        <v>319</v>
-      </c>
+      <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>320</v>
+        <v>275</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7445,7 +7437,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>278</v>
@@ -7493,7 +7485,7 @@
         <v>82</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>283</v>
@@ -7564,7 +7556,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>287</v>
@@ -7681,7 +7673,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>295</v>
@@ -7796,7 +7788,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>302</v>
@@ -7913,13 +7905,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>246</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>82</v>
@@ -7944,7 +7936,7 @@
         <v>247</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="M47" t="s" s="2">
         <v>249</v>
@@ -8032,7 +8024,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>257</v>
@@ -8147,7 +8139,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>258</v>
@@ -8264,7 +8256,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>259</v>
@@ -8312,7 +8304,7 @@
         <v>82</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>82</v>
@@ -8383,7 +8375,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>269</v>
@@ -8431,7 +8423,7 @@
         <v>82</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>82</v>
@@ -8448,11 +8440,9 @@
       <c r="X51" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="Y51" t="s" s="2">
-        <v>319</v>
-      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>320</v>
+        <v>275</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8502,7 +8492,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>278</v>
@@ -8550,7 +8540,7 @@
         <v>82</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>283</v>
@@ -8621,7 +8611,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>287</v>
@@ -8738,7 +8728,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>295</v>
@@ -8853,7 +8843,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>302</v>
@@ -8970,13 +8960,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>246</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>82</v>
@@ -9001,7 +8991,7 @@
         <v>247</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="M56" t="s" s="2">
         <v>249</v>
@@ -9089,7 +9079,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>257</v>
@@ -9204,7 +9194,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>258</v>
@@ -9321,7 +9311,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>259</v>
@@ -9369,7 +9359,7 @@
         <v>82</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>82</v>
@@ -9440,7 +9430,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>269</v>
@@ -9488,7 +9478,7 @@
         <v>82</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>82</v>
@@ -9505,11 +9495,9 @@
       <c r="X60" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="Y60" t="s" s="2">
-        <v>319</v>
-      </c>
+      <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>320</v>
+        <v>275</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9559,7 +9547,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>278</v>
@@ -9607,7 +9595,7 @@
         <v>82</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>283</v>
@@ -9678,7 +9666,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>287</v>
@@ -9795,7 +9783,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>295</v>
@@ -9910,7 +9898,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>302</v>
@@ -10027,13 +10015,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>246</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>82</v>
@@ -10058,7 +10046,7 @@
         <v>247</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="M65" t="s" s="2">
         <v>249</v>
@@ -10146,7 +10134,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>257</v>
@@ -10261,7 +10249,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>258</v>
@@ -10378,7 +10366,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>259</v>
@@ -10426,7 +10414,7 @@
         <v>82</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>82</v>
@@ -10497,7 +10485,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>269</v>
@@ -10545,7 +10533,7 @@
         <v>82</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>82</v>
@@ -10562,11 +10550,9 @@
       <c r="X69" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="Y69" t="s" s="2">
-        <v>319</v>
-      </c>
+      <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>320</v>
+        <v>275</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10616,7 +10602,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>278</v>
@@ -10735,7 +10721,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>287</v>
@@ -10852,7 +10838,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>295</v>
@@ -10967,7 +10953,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>302</v>
@@ -11084,13 +11070,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>246</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D74" t="s" s="2">
         <v>82</v>
@@ -11115,7 +11101,7 @@
         <v>247</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="M74" t="s" s="2">
         <v>249</v>
@@ -11203,7 +11189,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>257</v>
@@ -11318,7 +11304,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>258</v>
@@ -11435,7 +11421,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>259</v>
@@ -11483,7 +11469,7 @@
         <v>82</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>82</v>
@@ -11554,7 +11540,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>269</v>
@@ -11602,7 +11588,7 @@
         <v>82</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>82</v>
@@ -11619,11 +11605,9 @@
       <c r="X78" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="Y78" t="s" s="2">
-        <v>319</v>
-      </c>
+      <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>320</v>
+        <v>275</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>82</v>
@@ -11673,7 +11657,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>278</v>
@@ -11792,7 +11776,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>287</v>
@@ -11909,7 +11893,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>295</v>
@@ -12024,7 +12008,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>302</v>
@@ -12141,10 +12125,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12167,26 +12151,26 @@
         <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="N83" t="s" s="2">
+      <c r="P83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q83" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="O83" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="P83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q83" t="s" s="2">
-        <v>384</v>
-      </c>
       <c r="R83" t="s" s="2">
         <v>82</v>
       </c>
@@ -12230,7 +12214,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12245,13 +12229,13 @@
         <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>108</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>82</v>
@@ -12262,10 +12246,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12273,7 +12257,7 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>81</v>
@@ -12288,19 +12272,19 @@
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12337,7 +12321,7 @@
         <v>82</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AC84" s="2"/>
       <c r="AD84" t="s" s="2">
@@ -12347,7 +12331,7 @@
         <v>117</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12362,16 +12346,16 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12379,13 +12363,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D85" t="s" s="2">
         <v>82</v>
@@ -12407,19 +12391,19 @@
         <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="L85" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>401</v>
-      </c>
       <c r="N85" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12468,7 +12452,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12483,16 +12467,16 @@
         <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12500,10 +12484,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12615,10 +12599,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12732,10 +12716,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12761,16 +12745,16 @@
         <v>170</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="N88" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -12780,7 +12764,7 @@
         <v>82</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>82</v>
@@ -12798,28 +12782,28 @@
         <v>264</v>
       </c>
       <c r="Y88" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF88" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12834,7 +12818,7 @@
         <v>102</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>82</v>
@@ -12843,7 +12827,7 @@
         <v>82</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -12851,10 +12835,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12880,16 +12864,16 @@
         <v>104</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="N89" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="O89" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -12938,7 +12922,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12953,7 +12937,7 @@
         <v>102</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>82</v>
@@ -12962,7 +12946,7 @@
         <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -12970,14 +12954,14 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -12999,13 +12983,13 @@
         <v>104</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N90" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13055,7 +13039,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13070,7 +13054,7 @@
         <v>102</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>82</v>
@@ -13079,7 +13063,7 @@
         <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13087,14 +13071,14 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13116,13 +13100,13 @@
         <v>104</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N91" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13172,7 +13156,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13187,7 +13171,7 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>82</v>
@@ -13196,7 +13180,7 @@
         <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13204,10 +13188,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13233,10 +13217,10 @@
         <v>104</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13287,7 +13271,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13302,7 +13286,7 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>82</v>
@@ -13311,7 +13295,7 @@
         <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13319,10 +13303,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13348,10 +13332,10 @@
         <v>104</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13402,7 +13386,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13417,7 +13401,7 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>82</v>
@@ -13426,7 +13410,7 @@
         <v>82</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13434,10 +13418,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13463,14 +13447,14 @@
         <v>296</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13519,7 +13503,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13534,7 +13518,7 @@
         <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>82</v>
@@ -13543,7 +13527,7 @@
         <v>82</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13551,20 +13535,20 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>81</v>
@@ -13579,19 +13563,19 @@
         <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13640,7 +13624,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13655,16 +13639,16 @@
         <v>102</v>
       </c>
       <c r="AK95" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN95" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13672,10 +13656,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13787,10 +13771,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13904,13 +13888,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>82</v>
@@ -13932,13 +13916,13 @@
         <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -14021,10 +14005,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14050,16 +14034,16 @@
         <v>170</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="N99" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="O99" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
@@ -14087,28 +14071,28 @@
         <v>264</v>
       </c>
       <c r="Y99" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF99" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14123,7 +14107,7 @@
         <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>82</v>
@@ -14132,7 +14116,7 @@
         <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14140,10 +14124,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14169,16 +14153,16 @@
         <v>104</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="N100" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -14227,7 +14211,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14242,7 +14226,7 @@
         <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>82</v>
@@ -14251,7 +14235,7 @@
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14259,14 +14243,14 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14288,13 +14272,13 @@
         <v>104</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N101" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14344,7 +14328,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14359,7 +14343,7 @@
         <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>82</v>
@@ -14368,7 +14352,7 @@
         <v>82</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14376,14 +14360,14 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -14405,13 +14389,13 @@
         <v>104</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N102" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14461,7 +14445,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14476,7 +14460,7 @@
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>82</v>
@@ -14485,7 +14469,7 @@
         <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14493,10 +14477,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14522,10 +14506,10 @@
         <v>104</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14576,7 +14560,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14591,7 +14575,7 @@
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>82</v>
@@ -14600,7 +14584,7 @@
         <v>82</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14608,10 +14592,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14637,10 +14621,10 @@
         <v>104</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14691,7 +14675,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14706,7 +14690,7 @@
         <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>82</v>
@@ -14715,7 +14699,7 @@
         <v>82</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -14723,10 +14707,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14752,14 +14736,14 @@
         <v>296</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
@@ -14808,7 +14792,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14823,7 +14807,7 @@
         <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>82</v>
@@ -14832,7 +14816,7 @@
         <v>82</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -14840,10 +14824,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14866,19 +14850,19 @@
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="L106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="O106" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -14927,7 +14911,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14942,16 +14926,16 @@
         <v>102</v>
       </c>
       <c r="AK106" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN106" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -14959,10 +14943,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14988,16 +14972,16 @@
         <v>170</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="N107" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="O107" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>82</v>
@@ -15025,10 +15009,10 @@
         <v>264</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -15046,7 +15030,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15061,16 +15045,16 @@
         <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN107" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AL107" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AM107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15078,10 +15062,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15104,19 +15088,19 @@
         <v>91</v>
       </c>
       <c r="K108" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="L108" t="s" s="2">
+      <c r="N108" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="M108" t="s" s="2">
+      <c r="O108" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
@@ -15165,7 +15149,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15180,27 +15164,27 @@
         <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN108" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="AL108" t="s" s="2">
+      <c r="AO108" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>512</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15223,19 +15207,19 @@
         <v>91</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="N109" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="M109" t="s" s="2">
+      <c r="O109" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15284,7 +15268,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15299,7 +15283,7 @@
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>108</v>
@@ -15308,7 +15292,7 @@
         <v>82</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>
@@ -15316,10 +15300,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15345,16 +15329,16 @@
         <v>236</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="N110" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="O110" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15403,7 +15387,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15418,16 +15402,16 @@
         <v>102</v>
       </c>
       <c r="AK110" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN110" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="AL110" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN110" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
@@ -15435,10 +15419,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15464,14 +15448,14 @@
         <v>270</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15500,7 +15484,7 @@
       </c>
       <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>82</v>
@@ -15518,7 +15502,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15533,16 +15517,16 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN111" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="AL111" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN111" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -15550,10 +15534,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15576,19 +15560,19 @@
         <v>82</v>
       </c>
       <c r="K112" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="L112" t="s" s="2">
+      <c r="N112" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="M112" t="s" s="2">
+      <c r="O112" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -15637,7 +15621,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -15652,7 +15636,7 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>108</v>
@@ -15661,7 +15645,7 @@
         <v>82</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -15669,10 +15653,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15695,19 +15679,19 @@
         <v>82</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="L113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="O113" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>82</v>
@@ -15756,7 +15740,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -15771,7 +15755,7 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>108</v>
@@ -15780,7 +15764,7 @@
         <v>82</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -15788,10 +15772,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15814,19 +15798,19 @@
         <v>82</v>
       </c>
       <c r="K114" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="L114" t="s" s="2">
+      <c r="N114" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="M114" t="s" s="2">
+      <c r="O114" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>82</v>
@@ -15875,7 +15859,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -15887,10 +15871,10 @@
         <v>82</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>108</v>
@@ -15907,10 +15891,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16022,10 +16006,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16135,13 +16119,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B117" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="C117" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="C117" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="D117" t="s" s="2">
         <v>82</v>
@@ -16163,13 +16147,13 @@
         <v>82</v>
       </c>
       <c r="K117" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="L117" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -16252,13 +16236,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>82</v>
@@ -16280,13 +16264,13 @@
         <v>82</v>
       </c>
       <c r="K118" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="L118" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16369,14 +16353,14 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -16398,10 +16382,10 @@
         <v>111</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>114</v>
@@ -16456,7 +16440,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -16488,10 +16472,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16517,14 +16501,14 @@
         <v>270</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>82</v>
@@ -16552,16 +16536,16 @@
         <v>152</v>
       </c>
       <c r="Y120" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB120" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="Z120" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="AC120" s="2"/>
       <c r="AD120" t="s" s="2">
@@ -16571,7 +16555,7 @@
         <v>117</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -16586,7 +16570,7 @@
         <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="AL120" t="s" s="2">
         <v>108</v>
@@ -16595,7 +16579,7 @@
         <v>82</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>82</v>
@@ -16603,13 +16587,13 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>82</v>
@@ -16634,14 +16618,14 @@
         <v>270</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>82</v>
@@ -16670,7 +16654,7 @@
       </c>
       <c r="Y121" s="2"/>
       <c r="Z121" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>82</v>
@@ -16688,7 +16672,7 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -16703,7 +16687,7 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>108</v>
@@ -16712,7 +16696,7 @@
         <v>82</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>82</v>
@@ -16720,13 +16704,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>82</v>
@@ -16751,14 +16735,14 @@
         <v>270</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>82</v>
@@ -16787,7 +16771,7 @@
       </c>
       <c r="Y122" s="2"/>
       <c r="Z122" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>82</v>
@@ -16805,7 +16789,7 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -16820,7 +16804,7 @@
         <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>108</v>
@@ -16829,7 +16813,7 @@
         <v>82</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>82</v>
@@ -16837,10 +16821,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16863,17 +16847,17 @@
         <v>82</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>82</v>
@@ -16922,7 +16906,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -16937,7 +16921,7 @@
         <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>108</v>
@@ -16946,7 +16930,7 @@
         <v>82</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>82</v>
@@ -16954,10 +16938,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16980,19 +16964,19 @@
         <v>82</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="N124" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="M124" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>603</v>
-      </c>
       <c r="O124" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>82</v>
@@ -17041,7 +17025,7 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17056,7 +17040,7 @@
         <v>102</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="AL124" t="s" s="2">
         <v>108</v>
@@ -17065,7 +17049,7 @@
         <v>82</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>82</v>
@@ -17073,10 +17057,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17099,17 +17083,17 @@
         <v>82</v>
       </c>
       <c r="K125" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="L125" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>82</v>
@@ -17158,7 +17142,7 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17173,7 +17157,7 @@
         <v>102</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="AL125" t="s" s="2">
         <v>108</v>
@@ -17182,7 +17166,7 @@
         <v>82</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>82</v>
@@ -17190,10 +17174,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17219,14 +17203,14 @@
         <v>170</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>82</v>
@@ -17254,10 +17238,10 @@
         <v>264</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>82</v>
@@ -17275,7 +17259,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17290,7 +17274,7 @@
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>108</v>
@@ -17299,7 +17283,7 @@
         <v>82</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>82</v>
@@ -17307,10 +17291,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17336,14 +17320,14 @@
         <v>303</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>82</v>
@@ -17392,7 +17376,7 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17401,13 +17385,13 @@
         <v>90</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>108</v>
@@ -17416,7 +17400,7 @@
         <v>82</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>82</v>
@@ -17424,10 +17408,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17453,10 +17437,10 @@
         <v>296</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -17507,7 +17491,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -17522,7 +17506,7 @@
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>108</v>
@@ -17539,10 +17523,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17565,19 +17549,19 @@
         <v>82</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="N129" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="M129" t="s" s="2">
+      <c r="O129" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>82</v>
@@ -17626,7 +17610,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -17641,10 +17625,10 @@
         <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>82</v>
@@ -17658,10 +17642,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17773,10 +17757,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17890,14 +17874,14 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -17919,10 +17903,10 @@
         <v>111</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="N132" t="s" s="2">
         <v>114</v>
@@ -17977,7 +17961,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18009,10 +17993,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18038,16 +18022,16 @@
         <v>270</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="N133" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="M133" t="s" s="2">
+      <c r="O133" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>82</v>
@@ -18096,7 +18080,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>90</v>
@@ -18111,16 +18095,16 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AL133" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AM133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN133" t="s" s="2">
         <v>641</v>
-      </c>
-      <c r="AL133" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="AM133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN133" t="s" s="2">
-        <v>643</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>82</v>
@@ -18128,10 +18112,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18154,19 +18138,19 @@
         <v>82</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="N134" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="O134" t="s" s="2">
         <v>646</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>82</v>
@@ -18215,7 +18199,7 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18230,16 +18214,16 @@
         <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AL134" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="AM134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN134" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="AL134" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="AM134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN134" t="s" s="2">
-        <v>651</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>82</v>
@@ -18247,14 +18231,14 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
@@ -18273,16 +18257,16 @@
         <v>82</v>
       </c>
       <c r="K135" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="L135" t="s" s="2">
+      <c r="N135" t="s" s="2">
         <v>655</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -18332,7 +18316,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18347,7 +18331,7 @@
         <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>108</v>
@@ -18356,7 +18340,7 @@
         <v>82</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>82</v>
@@ -18364,10 +18348,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18390,19 +18374,19 @@
         <v>91</v>
       </c>
       <c r="K136" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="M136" t="s" s="2">
         <v>661</v>
       </c>
-      <c r="L136" t="s" s="2">
+      <c r="N136" t="s" s="2">
         <v>662</v>
       </c>
-      <c r="M136" t="s" s="2">
+      <c r="O136" t="s" s="2">
         <v>663</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>665</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>82</v>
@@ -18451,7 +18435,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -18466,10 +18450,10 @@
         <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>82</v>
@@ -18483,10 +18467,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18509,19 +18493,19 @@
         <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="L137" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="M137" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="N137" t="s" s="2">
         <v>668</v>
       </c>
-      <c r="M137" t="s" s="2">
+      <c r="O137" t="s" s="2">
         <v>669</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>671</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>82</v>
@@ -18570,7 +18554,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -18585,7 +18569,7 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>108</v>
@@ -18602,10 +18586,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18717,10 +18701,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18834,14 +18818,14 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -18863,10 +18847,10 @@
         <v>111</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="N140" t="s" s="2">
         <v>114</v>
@@ -18921,7 +18905,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -18953,10 +18937,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18979,16 +18963,16 @@
         <v>91</v>
       </c>
       <c r="K141" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="L141" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>677</v>
       </c>
-      <c r="L141" t="s" s="2">
+      <c r="N141" t="s" s="2">
         <v>678</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>680</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -19038,7 +19022,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>90</v>
@@ -19062,7 +19046,7 @@
         <v>82</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>82</v>
@@ -19070,10 +19054,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19099,10 +19083,10 @@
         <v>170</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -19132,10 +19116,10 @@
         <v>264</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>82</v>
@@ -19153,7 +19137,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>90</v>
@@ -19168,7 +19152,7 @@
         <v>102</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>108</v>
